--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/abr-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/abr-2026.xlsx
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>22981598.92</v>
+        <v>25595.22</v>
       </c>
     </row>
     <row r="3">
@@ -626,11 +626,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>58238195.4</v>
+        <v>64861.44</v>
       </c>
     </row>
     <row r="4">
@@ -687,11 +687,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>26442990</v>
+        <v>29450.27</v>
       </c>
     </row>
     <row r="5">
@@ -748,11 +748,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>34209990.29</v>
+        <v>38100.59</v>
       </c>
     </row>
     <row r="6">
@@ -809,11 +809,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>19412731.8</v>
+        <v>21620.48</v>
       </c>
     </row>
     <row r="7">
@@ -874,11 +874,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>113823500</v>
+        <v>126768.29</v>
       </c>
     </row>
     <row r="8">
@@ -935,11 +935,11 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>69736468.06</v>
+        <v>77667.38</v>
       </c>
     </row>
     <row r="9">
@@ -996,11 +996,11 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>55579405.77</v>
+        <v>61900.28</v>
       </c>
     </row>
     <row r="10">
@@ -1057,11 +1057,11 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>12286909.46</v>
+        <v>13684.26</v>
       </c>
     </row>
     <row r="11">
@@ -1118,11 +1118,11 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>27192690</v>
+        <v>30285.23</v>
       </c>
     </row>
     <row r="12">
@@ -1179,11 +1179,11 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>19356064</v>
+        <v>21557.37</v>
       </c>
     </row>
     <row r="13">
@@ -1240,11 +1240,11 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>37913400</v>
+        <v>42225.17</v>
       </c>
     </row>
     <row r="14">
@@ -1301,11 +1301,11 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>24218860.96</v>
+        <v>26973.2</v>
       </c>
     </row>
     <row r="15">
@@ -1362,11 +1362,11 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>37516588.55</v>
+        <v>41783.23</v>
       </c>
     </row>
     <row r="16">
@@ -1423,11 +1423,11 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>19625280.08</v>
+        <v>21857.2</v>
       </c>
     </row>
     <row r="17">
@@ -1484,11 +1484,11 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>37328534.04</v>
+        <v>41573.79</v>
       </c>
     </row>
     <row r="18">
@@ -1545,11 +1545,11 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>35625744</v>
+        <v>39677.35</v>
       </c>
     </row>
     <row r="19">
@@ -1606,11 +1606,11 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>38303100.01</v>
+        <v>42659.19</v>
       </c>
     </row>
     <row r="20">
@@ -1667,11 +1667,11 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>27192690</v>
+        <v>30285.23</v>
       </c>
     </row>
     <row r="21">
@@ -1728,11 +1728,11 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>12421932.81</v>
+        <v>13834.64</v>
       </c>
     </row>
     <row r="22">
@@ -1789,11 +1789,11 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>71251488</v>
+        <v>79354.7</v>
       </c>
     </row>
     <row r="23">
@@ -1850,11 +1850,11 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>12948273.38</v>
+        <v>14420.84</v>
       </c>
     </row>
     <row r="24">
@@ -1911,11 +1911,11 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>32552589.23</v>
+        <v>36254.69</v>
       </c>
     </row>
     <row r="25">
@@ -1972,11 +1972,11 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>32970505.33</v>
+        <v>36720.14</v>
       </c>
     </row>
     <row r="26">
@@ -2033,11 +2033,11 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>35625744</v>
+        <v>39677.35</v>
       </c>
     </row>
     <row r="27">
@@ -2094,11 +2094,11 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>12109430.48</v>
+        <v>13486.6</v>
       </c>
     </row>
     <row r="28">
@@ -2155,11 +2155,11 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>35332290</v>
+        <v>39350.52</v>
       </c>
     </row>
   </sheetData>
